--- a/docs/huyvu/XNT_HuyVu_2024.xlsx
+++ b/docs/huyvu/XNT_HuyVu_2024.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tháng 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tháng 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tháng 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tháng 4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tháng 5" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tháng 6" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Tháng 7" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Tháng 8" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Tháng 9" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tháng 10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Tháng 11" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Tháng 12" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Hoadon" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="xnt12thang" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 8" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 11" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 12" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoadon" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="xnt12thang" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/huyvu/XNT_HuyVu_2024.xlsx
+++ b/docs/huyvu/XNT_HuyVu_2024.xlsx
@@ -671,19 +671,19 @@
         <v>19914290.22117221</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>5959091</v>
+        <v>5645710.735587256</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>16957509.14487212</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>1272728</v>
+        <v>1053652.333447391</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>26390908</v>
+        <v>37404657.83738238</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>2148947.973358435</v>
@@ -695,25 +695,25 @@
         <v>7027640.669631639</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>10909091</v>
+        <v>21378350.12563742</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>727273</v>
+        <v>534458.7531409354</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>3581579.955597391</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>1563636</v>
+        <v>2658986.414817904</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>4539894.592365342</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>5636364</v>
+        <v>10750514.68095827</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>3581579.955597391</v>
@@ -725,19 +725,19 @@
         <v>4628773.918949948</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>3700000</v>
+        <v>5292754.508271186</v>
       </c>
       <c r="AE2" s="3" t="n">
         <v>9045467.000815652</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>6190908</v>
+        <v>7644122.54846119</v>
       </c>
       <c r="AG2" s="3" t="n">
         <v>6259406.289074737</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>23918176</v>
+        <v>40556483.04862697</v>
       </c>
     </row>
     <row r="3">
@@ -779,73 +779,73 @@
         <v>3326381.735820669</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>7181818</v>
+        <v>9261072.028683769</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>2045455</v>
+        <v>3087024.009561256</v>
       </c>
       <c r="O3" s="3" t="n">
         <v>11153938.28070292</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>8954547</v>
+        <v>10954782.91870965</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>3727274</v>
+        <v>4694906.965161277</v>
       </c>
       <c r="S3" s="3" t="n">
         <v>29735032.79513855</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>3536364</v>
+        <v>4759426.117907388</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>14528721.68164245</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>5818182</v>
+        <v>9420761.18670997</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>4347174.614927559</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>24100000</v>
+        <v>37870056.28797793</v>
       </c>
       <c r="Y3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>5590909</v>
+        <v>6311676.047996322</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>40528168.51908209</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>11009090</v>
+        <v>14331118.20619264</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>6885961.110544866</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>6300000</v>
+        <v>6345534.945094687</v>
       </c>
       <c r="AE3" s="3" t="n">
         <v>12108735.22515773</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>12213638</v>
+        <v>14257437.11800731</v>
       </c>
       <c r="AG3" s="3" t="n">
         <v>3907178.485377003</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>17404544</v>
+        <v>23593694.309548</v>
       </c>
     </row>
     <row r="4">
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1636364</v>
+        <v>2022987.351395938</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1190909</v>
+        <v>1517240.513546953</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>1000000</v>
+        <v>1011493.675697969</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>0</v>
@@ -917,13 +917,13 @@
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>1318182</v>
+        <v>1517240.513546953</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>1363636</v>
+        <v>1517240.513546953</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
@@ -935,25 +935,25 @@
         <v>0</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>9580001</v>
+        <v>11632177.27052664</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1670909</v>
+        <v>2528734.189244923</v>
       </c>
       <c r="AE4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>409091</v>
+        <v>505746.8378489845</v>
       </c>
       <c r="AG4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>4199996</v>
+        <v>5563215.21633883</v>
       </c>
     </row>
     <row r="5">
@@ -995,73 +995,73 @@
         <v>3115182.741801169</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4800002</v>
+        <v>4544171.702730658</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>7391958.982715005</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>5545455</v>
+        <v>6330463.718557539</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>3109092</v>
+        <v>2713055.879381803</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>3959977.749884586</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>3600002</v>
+        <v>3049980.561625193</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>4223976.976406253</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1700000</v>
+        <v>1432003.013227156</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>4223976.00841167</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>3200000</v>
+        <v>3215167.896592676</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>4223976.00841167</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>9450002</v>
+        <v>9982735.814003961</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>9635945.632187091</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6172731</v>
+        <v>6204589.641597013</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>5807967.495563338</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>8036372</v>
+        <v>8634379.759963937</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>5411969.623775421</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1972729</v>
+        <v>2108038.253453439</v>
       </c>
       <c r="AE5" s="3" t="n">
         <v>4223976.00841167</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1136365</v>
+        <v>1228130.804726808</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>4922684.178073766</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>34181891</v>
+        <v>43131245.04297827</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1103,7 @@
         <v>8421552.868566839</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4354546</v>
+        <v>1380191.748082146</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>923994.3888420843</v>
@@ -1115,19 +1115,19 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>345455</v>
+        <v>444854.1095475255</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>1108794.234605084</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>1063635</v>
+        <v>1286826.983946994</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>2032788.623447168</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>609090</v>
+        <v>809039.1628135405</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>923994.3888420843</v>
@@ -1139,37 +1139,37 @@
         <v>1108793.266610501</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>290909</v>
+        <v>385238.4525663679</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>2595985.29550278</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>318182</v>
+        <v>362896.8775704597</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>1671990.906660696</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>227273</v>
+        <v>350391.5608851168</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>2010789.010568557</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>290909</v>
+        <v>340511.6322716982</v>
       </c>
       <c r="AE6" s="3" t="n">
         <v>5200770.629755921</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>1145454</v>
+        <v>1397007.021363872</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>686404.9585173271</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>154545</v>
+        <v>331745.0234937831</v>
       </c>
     </row>
     <row r="7">
@@ -1319,73 +1319,73 @@
         <v>3722379.607608586</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4763643</v>
+        <v>6171344.416136706</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>3146963.218236788</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>5354546</v>
+        <v>3026486.73074434</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>3722379.607608586</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8072732</v>
+        <v>10665121.78360298</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>1755588.854802669</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>4154545</v>
+        <v>4823601.291650862</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>7286359.485705256</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>36745460</v>
+        <v>66916078.92412214</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>675850.9124688524</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>2499998</v>
+        <v>2850900.488947344</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>10490914</v>
+        <v>16214496.53088802</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>5236507.194649556</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>16368187</v>
+        <v>20640231.81362301</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>3898378.446626641</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>27072768</v>
+        <v>40379861.14490847</v>
       </c>
       <c r="AC8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>26200013</v>
+        <v>29716323.00276186</v>
       </c>
       <c r="AE8" s="3" t="n">
         <v>25311349.82439194</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>8390914</v>
+        <v>10215049.89261463</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>14763621</v>
+        <v>22787418.99121725</v>
       </c>
     </row>
     <row r="9">
@@ -1427,49 +1427,49 @@
         <v>17445118.99195131</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>2672726</v>
+        <v>6975010.096964863</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1227273</v>
+        <v>3487505.048482431</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>46515629.75101481</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>8699999</v>
+        <v>24482474.08430129</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>9776155.775497485</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>8136363</v>
+        <v>17079409.64232341</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>19139892.61910793</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>10181818</v>
+        <v>18216308.07889502</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>4768368.417705812</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>6500001</v>
+        <v>15419109.47206146</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>8340135.81221945</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8027272</v>
+        <v>6315177.301738932</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>37872096.89585396</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>16290910</v>
+        <v>29778804.67953072</v>
       </c>
       <c r="AA9" s="3" t="n">
         <v>22838193.3614745</v>
@@ -1535,73 +1535,73 @@
         <v>27116425.46624055</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>29309088</v>
+        <v>113462652.7200049</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>74927437.71470392</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>15218182</v>
+        <v>15450826.96496552</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>7317119.046872871</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>42681821</v>
+        <v>74955601.87275806</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>9019949.695623895</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>28090908</v>
+        <v>32572353.75634686</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>83832730.38800873</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>9309091</v>
+        <v>12689658.33912366</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>298239128.9611882</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>37887880</v>
+        <v>47115437.98278801</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>13663636</v>
+        <v>13960129.77267793</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>6350131.581328349</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>22759092</v>
+        <v>72958235.77097823</v>
       </c>
       <c r="AA10" s="3" t="n">
         <v>6723064.078202219</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>29936363</v>
+        <v>33003834.30327942</v>
       </c>
       <c r="AC10" s="3" t="n">
         <v>6030359.410941371</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>71031818</v>
+        <v>79811942.10025826</v>
       </c>
       <c r="AE10" s="3" t="n">
         <v>17173361.59077227</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>58538722</v>
+        <v>57492370.24559185</v>
       </c>
       <c r="AG10" s="3" t="n">
         <v>3857071.213803613</v>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>26363637</v>
+        <v>94042913.79269917</v>
       </c>
     </row>
     <row r="11">
@@ -1643,73 +1643,73 @@
         <v>49249804.54822595</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>49936364</v>
+        <v>34787964.07665252</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>588716.8812311169</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>4636364</v>
+        <v>5891358.072951676</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>234093359.1043832</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>81963471</v>
+        <v>76483103.61040494</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>59052266.5445</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>59999999</v>
+        <v>59443590.48203214</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>47041929.10356777</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>35140404</v>
+        <v>41890735.90757672</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>160494438.7066026</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>7318182</v>
+        <v>3106715.040046893</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>12677209.40367764</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>114563635</v>
+        <v>201055703.8470454</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>11536735.61036801</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>2527273</v>
+        <v>3073298.887627897</v>
       </c>
       <c r="AA11" s="3" t="n">
         <v>34438474.61458922</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>46718184</v>
+        <v>62847413.9501529</v>
       </c>
       <c r="AC11" s="3" t="n">
         <v>56383924.62194292</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>23818182</v>
+        <v>27476596.69206852</v>
       </c>
       <c r="AE11" s="3" t="n">
         <v>32647817.54966516</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>50972728</v>
+        <v>63897623.78210942</v>
       </c>
       <c r="AG11" s="3" t="n">
         <v>71971401.83124425</v>
       </c>
       <c r="AH11" s="3" t="n">
-        <v>21345454</v>
+        <v>24567950.96617375</v>
       </c>
     </row>
     <row r="12">
@@ -1751,31 +1751,31 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>6354546</v>
+        <v>6647257.327004643</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>6283164.748109921</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>4627273</v>
+        <v>6727522.417079032</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>32260619.71662761</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10745455</v>
+        <v>13269449.41669652</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>5807967.495563338</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>11372727</v>
+        <v>13344587.38606427</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>3854378.252874836</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>5640909</v>
+        <v>6592838.991081066</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>15267914.28873237</v>
@@ -1787,7 +1787,7 @@
         <v>5895966.915072366</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>7763637</v>
+        <v>6767081.809179887</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>22343074.78041813</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>2372727</v>
+        <v>3546506.116572679</v>
       </c>
       <c r="AC12" s="3" t="n">
         <v>6371164.167618949</v>
@@ -1871,7 +1871,7 @@
         <v>1759990.326169723</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>2081818</v>
+        <v>1906466.029095888</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         <v>6995961.110927088</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>7881819</v>
+        <v>8664585.289381864</v>
       </c>
       <c r="AA14" s="3" t="n">
         <v>0</v>
@@ -2075,73 +2075,73 @@
         <v>3079982.586799724</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>6060000</v>
+        <v>5939134.46501935</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>10195421.00798026</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>3514546</v>
+        <v>1360296.168787992</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>4866390.453123018</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>5272729</v>
+        <v>6357465.640444922</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>13389120.05145174</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>9369999</v>
+        <v>4310993.617121229</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>10603940.21478098</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>4963634</v>
+        <v>6037959.219005461</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>4678921.78664998</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>7445453</v>
+        <v>4404298.619795488</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>3727659.050062053</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>7454545</v>
+        <v>7611274.741781331</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>22893732.22086789</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>4636364</v>
+        <v>5552042.882017856</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>7622519.804375548</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>2283634</v>
+        <v>3867162.555235251</v>
       </c>
       <c r="AC15" s="3" t="n">
         <v>4480934.042339548</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>14736366</v>
+        <v>15762772.37125169</v>
       </c>
       <c r="AE15" s="3" t="n">
         <v>15853061.20594288</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>2993637</v>
+        <v>3758074.963980461</v>
       </c>
       <c r="AG15" s="3" t="n">
         <v>6017409.579415429</v>
       </c>
       <c r="AH15" s="3" t="n">
-        <v>13209091</v>
+        <v>19396078.32770029</v>
       </c>
     </row>
     <row r="16">
@@ -2183,73 +2183,73 @@
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3404546</v>
+        <v>4015554.457654906</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1290910</v>
+        <v>1606221.783061963</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3840911</v>
+        <v>4130284.585016476</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>17269906.16453432</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>3368181</v>
+        <v>4036796.685454171</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>34951817</v>
+        <v>93213305.28230542</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>116866862.9596521</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2227279</v>
+        <v>4049157.913313672</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>9086364</v>
+        <v>15021069.67842169</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>15077277</v>
+        <v>18417137.60571703</v>
       </c>
       <c r="AA16" s="3" t="n">
         <v>4135977.556897225</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>9518180</v>
+        <v>9460572.358647419</v>
       </c>
       <c r="AC16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>4040910</v>
+        <v>6262632.406428573</v>
       </c>
       <c r="AE16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>4309994</v>
+        <v>6129384.908419456</v>
       </c>
       <c r="AG16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH16" s="3" t="n">
-        <v>15813632</v>
+        <v>22518827.16354105</v>
       </c>
     </row>
     <row r="17">
@@ -2291,73 +2291,73 @@
         <v>256745000.5841249</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>286377374</v>
+        <v>329158002.6579762</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>141808546.3796843</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>75377438</v>
+        <v>34737555.63108806</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>198442421.6439793</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>384933627</v>
+        <v>446386006.0982314</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>291293298.3537045</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>395837153</v>
+        <v>213497796.7342614</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>148183068.4417178</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>229219596</v>
+        <v>191170924.4246266</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>207484341.7063395</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>188482083</v>
+        <v>69173329.36387223</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>222110682.9439576</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>1033183894</v>
+        <v>632045854.1710213</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>177776379.7428921</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>465525420</v>
+        <v>221328153.2144486</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>322155324.9472123</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>431022654</v>
+        <v>450094181.2889934</v>
       </c>
       <c r="AC17" s="3" t="n">
         <v>265047053.5534759</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>323007429</v>
+        <v>300697865.0412976</v>
       </c>
       <c r="AE17" s="3" t="n">
         <v>325585123.7207146</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>310354916</v>
+        <v>157024516.2567831</v>
       </c>
       <c r="AG17" s="3" t="n">
         <v>276981707.8947937</v>
       </c>
       <c r="AH17" s="3" t="n">
-        <v>615179223</v>
+        <v>244512311.4686213</v>
       </c>
     </row>
     <row r="18">
@@ -2435,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>17727272</v>
+        <v>19438759.08227341</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>0</v>
@@ -2519,13 +2519,13 @@
         <v>0</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>3454545</v>
+        <v>3545244.633645741</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>16315108.25208493</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>9409091</v>
+        <v>11030036.10827052</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>30163640</v>
+        <v>43506266.05106054</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>6297245.197308332</v>
@@ -2627,61 +2627,61 @@
         <v>60279662.37934824</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>30345455</v>
+        <v>16610896.886672</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>28309090</v>
+        <v>33221793.77334399</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>133368503.6008926</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>215672727</v>
+        <v>144401127.7177483</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>188318946.5082633</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>49145455</v>
+        <v>90948647.32443187</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>79104517.28957266</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>103590909</v>
+        <v>94515715.01193079</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>456629444.7257888</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>374327272</v>
+        <v>616232837.3089584</v>
       </c>
       <c r="AA20" s="3" t="n">
         <v>269718489.8976645</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>190418180</v>
+        <v>326794140.1380389</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>251414595.1518734</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>104300000</v>
+        <v>98492416.86645402</v>
       </c>
       <c r="AE20" s="3" t="n">
         <v>348126053.0237587</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>227718182</v>
+        <v>176001333.3913915</v>
       </c>
       <c r="AG20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH20" s="3" t="n">
-        <v>407509089</v>
+        <v>300237568.7264915</v>
       </c>
     </row>
     <row r="21">
@@ -2753,13 +2753,13 @@
         <v>23407868.8212714</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>12590909</v>
+        <v>15153690.69670728</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>24490909</v>
+        <v>30307381.39341456</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>11181818</v>
+        <v>15153690.69670728</v>
       </c>
       <c r="AC21" s="3" t="n">
         <v>0</v>
@@ -2783,13 +2783,13 @@
         <v>9767945.245447924</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>11809091</v>
+        <v>14919722.9121507</v>
       </c>
       <c r="AG21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH21" s="3" t="n">
-        <v>34454546</v>
+        <v>29839445.8243014</v>
       </c>
     </row>
     <row r="22">
@@ -2885,7 +2885,7 @@
         <v>12319931.31519348</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>47272729</v>
+        <v>63299634.17402625</v>
       </c>
       <c r="AE22" s="3" t="n">
         <v>0</v>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>14136363</v>
+        <v>14355126.37037596</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>20591884.49299876</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>39572726</v>
+        <v>42736855.43563785</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>0</v>
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>56545455</v>
+        <v>71228092.39272971</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>37045455</v>
+        <v>43573518.1409544</v>
       </c>
       <c r="AA24" s="3" t="n">
         <v>0</v>
@@ -3173,19 +3173,19 @@
         <v>19510630.67226306</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>43307914</v>
+        <v>27956917.39215437</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>5467376.665688512</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8181818</v>
+        <v>5630572.658159561</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>32727273</v>
+        <v>16891717.97447868</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>0</v>
@@ -3197,13 +3197,13 @@
         <v>11831044.68325985</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>26532323</v>
+        <v>17232513.36014473</v>
       </c>
       <c r="AA25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>24354545</v>
+        <v>11488342.24009649</v>
       </c>
       <c r="AC25" s="3" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>8095954.338787229</v>
       </c>
       <c r="AH25" s="3" t="n">
-        <v>9954546</v>
+        <v>5895220.556812839</v>
       </c>
     </row>
     <row r="26">
@@ -3263,7 +3263,7 @@
         <v>71709038.67855534</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>18701818</v>
+        <v>20483877.71644859</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>0</v>
@@ -3275,13 +3275,13 @@
         <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>31127272</v>
+        <v>40967755.43289718</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>33445455</v>
+        <v>40967755.43289718</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>0</v>
@@ -3299,13 +3299,13 @@
         <v>19623889.91040488</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>59590909</v>
+        <v>82888151.83159874</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>17063636</v>
+        <v>20722037.95789969</v>
       </c>
       <c r="AA26" s="3" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>71015603.17538464</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>46590909</v>
+        <v>22654357.98218965</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>0</v>
@@ -3395,37 +3395,37 @@
         <v>0</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>17863636</v>
+        <v>7551452.660729882</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>149611481.9035658</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>84500001</v>
+        <v>111691105.9065586</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>36167797.23401003</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>55909090</v>
+        <v>22776328.63287485</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>188846943.0253175</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>197681818</v>
+        <v>141021720.2302819</v>
       </c>
       <c r="AA27" s="3" t="n">
         <v>66879625.61848741</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>57818182</v>
+        <v>59721046.48157743</v>
       </c>
       <c r="AC27" s="3" t="n">
         <v>74130784.94919123</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>92090910</v>
+        <v>44290644.87631413</v>
       </c>
       <c r="AE27" s="3" t="n">
         <v>86697114.44541106</v>
@@ -3437,7 +3437,7 @@
         <v>454975053.8966289</v>
       </c>
       <c r="AH27" s="3" t="n">
-        <v>16627273</v>
+        <v>12551425.17047498</v>
       </c>
     </row>
     <row r="28">
@@ -3479,73 +3479,73 @@
         <v>30019272.78838225</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>18409091</v>
+        <v>26050733.34353263</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>112384171.0391506</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>31309090</v>
+        <v>52395575.37936204</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>331450139.3109307</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>154554546</v>
+        <v>235350640.1749429</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>28354545</v>
+        <v>39225106.69582382</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>83854545</v>
+        <v>117675320.0874715</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>684636165.2484233</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>135545454</v>
+        <v>196451148.2915423</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>485493287.2365658</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>561372725</v>
+        <v>671891098.7973359</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>103839419.5640679</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>109036364</v>
+        <v>158186432.5029855</v>
       </c>
       <c r="AA28" s="3" t="n">
         <v>83071535.26405644</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>100163633</v>
+        <v>118695104.9600402</v>
       </c>
       <c r="AC28" s="3" t="n">
         <v>131031266.3282112</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>221036362</v>
+        <v>304289702.2665111</v>
       </c>
       <c r="AE28" s="3" t="n">
         <v>230998707.5619035</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>126127272</v>
+        <v>146983329.9179977</v>
       </c>
       <c r="AG28" s="3" t="n">
         <v>297825529.0759104</v>
       </c>
       <c r="AH28" s="3" t="n">
-        <v>138698184</v>
+        <v>172868541.9468878</v>
       </c>
     </row>
     <row r="29">
@@ -3587,73 +3587,73 @@
         <v>115305753.8964384</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>34172728</v>
+        <v>39777295.13050961</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>342752801.2472979</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>114181818</v>
+        <v>146041367.2894526</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>194227230.1864046</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>225581817</v>
+        <v>298684127.1977079</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>21368039.00523045</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>32127273</v>
+        <v>38980387.53766825</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>93854546</v>
+        <v>116941162.6130048</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>316651267.7651888</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>166527272</v>
+        <v>269853109.0529957</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>129676075.8485689</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>181436365</v>
+        <v>240992116.5199594</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>11792813.73722031</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>65649999</v>
+        <v>76172980.88832898</v>
       </c>
       <c r="AA29" s="3" t="n">
         <v>519794605.0603749</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>324445454</v>
+        <v>386393221.8779246</v>
       </c>
       <c r="AC29" s="3" t="n">
         <v>25247939.40326996</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>167772730</v>
+        <v>193639211.5652541</v>
       </c>
       <c r="AE29" s="3" t="n">
         <v>79934352.90937667</v>
       </c>
       <c r="AF29" s="3" t="n">
-        <v>183009093</v>
+        <v>207459387.3949896</v>
       </c>
       <c r="AG29" s="3" t="n">
         <v>457069441.8233339</v>
       </c>
       <c r="AH29" s="3" t="n">
-        <v>383463636</v>
+        <v>303555949.2219083</v>
       </c>
     </row>
     <row r="30">
@@ -3707,43 +3707,43 @@
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>11645455</v>
+        <v>5151913.026367184</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>9163636</v>
+        <v>4121530.421093747</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8709091</v>
+        <v>4121530.421093747</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>4709091</v>
+        <v>2060765.210546873</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>2354545</v>
+        <v>1030382.605273437</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1495992.06764264</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>7063636</v>
+        <v>2537763.43315999</v>
       </c>
       <c r="AA30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>2354545</v>
+        <v>751929.9061214785</v>
       </c>
       <c r="AC30" s="3" t="n">
         <v>0</v>
@@ -3815,7 +3815,7 @@
         <v>73215590.5990995</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>30254546</v>
+        <v>35668930.79457366</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>0</v>
@@ -3833,13 +3833,13 @@
         <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>45409092</v>
+        <v>53503396.19186049</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>28681818</v>
+        <v>35668930.79457366</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>10454545</v>
+        <v>17834465.39728683</v>
       </c>
       <c r="AC31" s="3" t="n">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>2393586.340233641</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>17809091</v>
+        <v>2561997.569518835</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>2345454</v>
+        <v>2561997.569518835</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>18999093.93509132</v>
@@ -3977,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3" t="n">
-        <v>36181818</v>
+        <v>4244322.709648638</v>
       </c>
     </row>
     <row r="33">
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>1636364</v>
+        <v>1794347.490878311</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>0</v>
@@ -4127,73 +4127,73 @@
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>13318182</v>
+        <v>12175969.29440534</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>5244770.823507726</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>10627273</v>
+        <v>5999111.235033751</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>41324569.60600331</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>34672728</v>
+        <v>26149886.05748377</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>45217668.61017648</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>39300001</v>
+        <v>26191395.58532304</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>55818181</v>
+        <v>47144512.05358148</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12302331.23769276</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>7272727</v>
+        <v>5035868.497755802</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>13863636</v>
+        <v>15107605.49326741</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>15787111.73503076</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>12809091</v>
+        <v>19158048.0725938</v>
       </c>
       <c r="AA34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>3136363</v>
+        <v>9579024.0362969</v>
       </c>
       <c r="AC34" s="3" t="n">
         <v>25871855.47150794</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>45981819</v>
+        <v>30194886.25898965</v>
       </c>
       <c r="AE34" s="3" t="n">
         <v>42151765.50458059</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>55445454</v>
+        <v>32464324.5626086</v>
       </c>
       <c r="AG34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH34" s="3" t="n">
-        <v>2045455</v>
+        <v>5410720.760434768</v>
       </c>
     </row>
     <row r="35">
@@ -4235,73 +4235,73 @@
         <v>54174258.2203967</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>40036363</v>
+        <v>61652760.4856622</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>68958173.28184296</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>53172727</v>
+        <v>45762526.70801412</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>151121555.3884015</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>69336363</v>
+        <v>90658011.08727378</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>2859983.554029863</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>32053636</v>
+        <v>60075933.66073723</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>15707912.3542721</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>194409093</v>
+        <v>256042949.9511672</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>151834350.783224</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>31981818</v>
+        <v>44430970.31385165</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>61775655.41498546</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>200963637</v>
+        <v>282247078.0877665</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>278324842.6119943</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>218990907</v>
+        <v>271911904.1636609</v>
       </c>
       <c r="AA35" s="3" t="n">
         <v>289606378.0665964</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>75145454</v>
+        <v>107932071.8555778</v>
       </c>
       <c r="AC35" s="3" t="n">
         <v>23231869.98225335</v>
       </c>
       <c r="AD35" s="3" t="n">
-        <v>18000000</v>
+        <v>15411526.38905219</v>
       </c>
       <c r="AE35" s="3" t="n">
         <v>16191909.64556904</v>
       </c>
       <c r="AF35" s="3" t="n">
-        <v>42509090</v>
+        <v>77275307.23234576</v>
       </c>
       <c r="AG35" s="3" t="n">
         <v>782997619.2540636</v>
       </c>
       <c r="AH35" s="3" t="n">
-        <v>126418182</v>
+        <v>144759572.8766888</v>
       </c>
     </row>
     <row r="36">
@@ -4355,7 +4355,7 @@
         <v>5543969.237036254</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>6045455</v>
+        <v>20247426.3313</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0</v>
@@ -4373,37 +4373,37 @@
         <v>0</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>37227273</v>
+        <v>40494852.6626</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>34847804.97338002</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>14090909</v>
+        <v>20446758.53674602</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>194822990.1962187</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>106500000</v>
+        <v>127554868.3258596</v>
       </c>
       <c r="AA36" s="3" t="n">
         <v>105511408.5347394</v>
       </c>
       <c r="AB36" s="3" t="n">
-        <v>34818182</v>
+        <v>43039057.2618696</v>
       </c>
       <c r="AC36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AD36" s="3" t="n">
-        <v>13636364</v>
+        <v>21519528.6309348</v>
       </c>
       <c r="AE36" s="3" t="n">
         <v>5499969.043284449</v>
       </c>
       <c r="AF36" s="3" t="n">
-        <v>38009090</v>
+        <v>63114968.88429185</v>
       </c>
       <c r="AG36" s="3" t="n">
         <v>0</v>
@@ -4463,19 +4463,19 @@
         <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>10272728</v>
+        <v>11093330.26120391</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>5136364</v>
+        <v>5546665.130601955</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>6809091</v>
+        <v>11093330.26120391</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>14924258.78800905</v>
@@ -4493,31 +4493,31 @@
         <v>29107034.69374577</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>10900000</v>
+        <v>11131509.91021957</v>
       </c>
       <c r="AA37" s="3" t="n">
         <v>50444380.52675134</v>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>8063636</v>
+        <v>10937089.65070758</v>
       </c>
       <c r="AC37" s="3" t="n">
         <v>37223615.06109891</v>
       </c>
       <c r="AD37" s="3" t="n">
-        <v>10709090</v>
+        <v>10776482.42351157</v>
       </c>
       <c r="AE37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AF37" s="3" t="n">
-        <v>5354545</v>
+        <v>5388241.211755783</v>
       </c>
       <c r="AG37" s="3" t="n">
         <v>277631584.2518322</v>
       </c>
       <c r="AH37" s="3" t="n">
-        <v>31227272</v>
+        <v>51410502.61910744</v>
       </c>
     </row>
     <row r="38">
@@ -4559,73 +4559,73 @@
         <v>55427369.79932612</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>13190910</v>
+        <v>18872264.87158209</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>5563636</v>
+        <v>7548905.948632835</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>84539367.40129685</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>40672728</v>
+        <v>56154163.65064899</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>8072728</v>
+        <v>11230832.7301298</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17812827.22206292</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>13800001</v>
+        <v>18724462.40649775</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>87329690.19318493</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>8154546</v>
+        <v>11151764.28747044</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>57218182</v>
+        <v>85496859.53727335</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>73979974.29720683</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>62472727</v>
+        <v>89354567.92365262</v>
       </c>
       <c r="AA38" s="3" t="n">
         <v>175446669.7402851</v>
       </c>
       <c r="AB38" s="3" t="n">
-        <v>28399999</v>
+        <v>37289873.18577852</v>
       </c>
       <c r="AC38" s="3" t="n">
         <v>172530432.1490824</v>
       </c>
       <c r="AD38" s="3" t="n">
-        <v>75100002</v>
+        <v>98695451.19377732</v>
       </c>
       <c r="AE38" s="3" t="n">
         <v>188565174.3222432</v>
       </c>
       <c r="AF38" s="3" t="n">
-        <v>68009091</v>
+        <v>88853208.89309247</v>
       </c>
       <c r="AG38" s="3" t="n">
         <v>617831819.8055353</v>
       </c>
       <c r="AH38" s="3" t="n">
-        <v>377613615</v>
+        <v>488865396.4239828</v>
       </c>
     </row>
     <row r="39">
@@ -4667,73 +4667,73 @@
         <v>30653605.44632353</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>35492725</v>
+        <v>61830079.99327102</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>8346753.023186062</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>28963637</v>
+        <v>17883171.06432905</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>21889877.14075015</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>232436356</v>
+        <v>185439769.1340472</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>61397255.6847091</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>114227273</v>
+        <v>56747837.14043161</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>79987153.14187883</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>393218183</v>
+        <v>270192087.742233</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>48069747.52044488</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>49545455</v>
+        <v>29695495.73942848</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>38358982.68298537</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>83099999</v>
+        <v>49824650.86061336</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>80981544.93674006</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>49463635</v>
+        <v>28392940.75184952</v>
       </c>
       <c r="AA39" s="3" t="n">
         <v>36273397.69901436</v>
       </c>
       <c r="AB39" s="3" t="n">
-        <v>56454544</v>
+        <v>42898634.51592483</v>
       </c>
       <c r="AC39" s="3" t="n">
         <v>34073408.33931033</v>
       </c>
       <c r="AD39" s="3" t="n">
-        <v>33181816</v>
+        <v>24851963.10391542</v>
       </c>
       <c r="AE39" s="3" t="n">
         <v>58176475.38188735</v>
       </c>
       <c r="AF39" s="3" t="n">
-        <v>65793637</v>
+        <v>26846087.92844785</v>
       </c>
       <c r="AG39" s="3" t="n">
         <v>111196174.5198031</v>
       </c>
       <c r="AH39" s="3" t="n">
-        <v>110345455</v>
+        <v>46789823.72344588</v>
       </c>
     </row>
     <row r="40">
@@ -4811,13 +4811,13 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>4545455</v>
+        <v>5508403.047854347</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6354545</v>
+        <v>5508403.047854347</v>
       </c>
       <c r="AA40" s="3" t="n">
         <v>0</v>
@@ -4889,13 +4889,13 @@
         <v>11061538.35782143</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>6863636</v>
+        <v>7053673.821739321</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>31761663.03705126</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>19254545</v>
+        <v>20997579.73416812</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>0</v>
@@ -4925,13 +4925,13 @@
         <v>21753477.99211143</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6909091</v>
+        <v>7002889.408976076</v>
       </c>
       <c r="AA41" s="3" t="n">
         <v>7963955.693520978</v>
       </c>
       <c r="AB41" s="3" t="n">
-        <v>13636364</v>
+        <v>6873610.961548328</v>
       </c>
       <c r="AC41" s="3" t="n">
         <v>10911938.66705987</v>
@@ -4943,13 +4943,13 @@
         <v>0</v>
       </c>
       <c r="AF41" s="3" t="n">
-        <v>6272727</v>
+        <v>6883816.34626486</v>
       </c>
       <c r="AG41" s="3" t="n">
         <v>21190280.35206124</v>
       </c>
       <c r="AH41" s="3" t="n">
-        <v>12709090</v>
+        <v>13752814.38547117</v>
       </c>
     </row>
     <row r="42">
@@ -5003,43 +5003,43 @@
         <v>16323908.29083529</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>13563636</v>
+        <v>5962183.845894032</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>615996.9045577779</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>12536363</v>
+        <v>5658134.010009227</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>5675968.850297087</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>6636364</v>
+        <v>5755304.188628223</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>14123918.93113126</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>409091</v>
+        <v>2689632.432660871</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>219999.0327698611</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>2254545</v>
+        <v>2630942.243837443</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>2727984.908763613</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>7472727</v>
+        <v>9666758.749450099</v>
       </c>
       <c r="AA42" s="3" t="n">
         <v>1187992.647369168</v>
       </c>
       <c r="AB42" s="3" t="n">
-        <v>354546</v>
+        <v>2187266.995001056</v>
       </c>
       <c r="AC42" s="3" t="n">
         <v>0</v>
@@ -5051,13 +5051,13 @@
         <v>439997.0975451395</v>
       </c>
       <c r="AF42" s="3" t="n">
-        <v>490909</v>
+        <v>4212497.145113912</v>
       </c>
       <c r="AG42" s="3" t="n">
         <v>1520280.019714503</v>
       </c>
       <c r="AH42" s="3" t="n">
-        <v>872728</v>
+        <v>3650533.590321449</v>
       </c>
     </row>
     <row r="43">
@@ -5117,19 +5117,19 @@
         <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>1727273</v>
+        <v>1631357.705517516</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>772727</v>
+        <v>815678.8527587581</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>9818182</v>
+        <v>10603825.08586385</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>990909</v>
+        <v>815678.8527587581</v>
       </c>
       <c r="AA43" s="3" t="n">
         <v>5785967.882684726</v>
@@ -5153,19 +5153,19 @@
         <v>8909950.663236257</v>
       </c>
       <c r="AD43" s="3" t="n">
-        <v>1200000</v>
+        <v>1615077.309307433</v>
       </c>
       <c r="AE43" s="3" t="n">
         <v>86925915.45292045</v>
       </c>
       <c r="AF43" s="3" t="n">
-        <v>1909091</v>
+        <v>2382232.469710655</v>
       </c>
       <c r="AG43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH43" s="3" t="n">
-        <v>545454</v>
+        <v>794077.4899035516</v>
       </c>
     </row>
     <row r="44">
@@ -5231,19 +5231,19 @@
         <v>0</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>1136363</v>
+        <v>919733.8174773039</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>12454546</v>
+        <v>14255874.17089821</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>3099998</v>
+        <v>2299334.54369326</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>3475980.458587641</v>
@@ -5255,25 +5255,25 @@
         <v>10322343.81474234</v>
       </c>
       <c r="AB44" s="3" t="n">
-        <v>6963636</v>
+        <v>10005329.61178101</v>
       </c>
       <c r="AC44" s="3" t="n">
         <v>7519556.156614201</v>
       </c>
       <c r="AD44" s="3" t="n">
-        <v>5145452</v>
+        <v>6797872.697656883</v>
       </c>
       <c r="AE44" s="3" t="n">
         <v>82772334.91453876</v>
       </c>
       <c r="AF44" s="3" t="n">
-        <v>5054544</v>
+        <v>4342671.865789458</v>
       </c>
       <c r="AG44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH44" s="3" t="n">
-        <v>13309088</v>
+        <v>19107756.20947361</v>
       </c>
     </row>
     <row r="45">
@@ -5333,55 +5333,55 @@
         <v>11703935.37863029</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>6536364</v>
+        <v>10100078.70296132</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>82059544.35968909</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>91772730</v>
+        <v>110073475.5566103</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>31195824.70777975</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>22427274</v>
+        <v>29451389.48454379</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>13578324.27256554</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>23618182</v>
+        <v>29325103.41519845</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>17723101.86821312</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>15763636</v>
+        <v>19295179.26712192</v>
       </c>
       <c r="AA45" s="3" t="n">
         <v>19386291.76812888</v>
       </c>
       <c r="AB45" s="3" t="n">
-        <v>25718182</v>
+        <v>28713422.04148351</v>
       </c>
       <c r="AC45" s="3" t="n">
         <v>69959608.20528713</v>
       </c>
       <c r="AD45" s="3" t="n">
-        <v>87163636</v>
+        <v>60991223.62801452</v>
       </c>
       <c r="AE45" s="3" t="n">
         <v>19623890.87839946</v>
       </c>
       <c r="AF45" s="3" t="n">
-        <v>14409091</v>
+        <v>20129554.53726867</v>
       </c>
       <c r="AG45" s="3" t="n">
         <v>15135915.64346612</v>
       </c>
       <c r="AH45" s="3" t="n">
-        <v>50372727</v>
+        <v>60315261.60310473</v>
       </c>
     </row>
     <row r="46">
@@ -5423,73 +5423,73 @@
         <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>20954546</v>
+        <v>7172623.447622869</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>4751973.493460421</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>1454545</v>
+        <v>1104927.395807446</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>141679206.736744</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>36363640</v>
+        <v>46175271.49120322</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>1091194.157104362</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>9363635</v>
+        <v>7616341.024595102</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>4954546</v>
+        <v>3808170.512297551</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>1073594.07960364</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>8945455</v>
+        <v>8172045.709216502</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>40998970.10822912</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>85481822</v>
+        <v>74245416.89550915</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>1135193.382861584</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2999998</v>
+        <v>3561740.361070385</v>
       </c>
       <c r="AA46" s="3" t="n">
         <v>30597427.88072269</v>
       </c>
       <c r="AB46" s="3" t="n">
-        <v>64990889</v>
+        <v>105107978.7801289</v>
       </c>
       <c r="AC46" s="3" t="n">
         <v>29435836.31759919</v>
       </c>
       <c r="AD46" s="3" t="n">
-        <v>28249997</v>
+        <v>43650009.88676928</v>
       </c>
       <c r="AE46" s="3" t="n">
         <v>223518745.2877011</v>
       </c>
       <c r="AF46" s="3" t="n">
-        <v>8481817</v>
+        <v>10517571.34024101</v>
       </c>
       <c r="AG46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH46" s="3" t="n">
-        <v>51027265</v>
+        <v>73622999.38168706</v>
       </c>
     </row>
     <row r="47">
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>863637</v>
+        <v>1004090.540953585</v>
       </c>
       <c r="M47" s="3" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>2411186.417734363</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>4363637</v>
+        <v>4054859.121379705</v>
       </c>
       <c r="Q47" s="3" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="3" t="n">
-        <v>1363636</v>
+        <v>1013714.780344926</v>
       </c>
       <c r="U47" s="3" t="n">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="X47" s="3" t="n">
-        <v>3090909</v>
+        <v>4054859.121379705</v>
       </c>
       <c r="Y47" s="3" t="n">
         <v>0</v>
@@ -5579,25 +5579,25 @@
         <v>12935927.25175668</v>
       </c>
       <c r="AB47" s="3" t="n">
-        <v>31818182</v>
+        <v>1969601.78105196</v>
       </c>
       <c r="AC47" s="3" t="n">
         <v>14053520.55711754</v>
       </c>
       <c r="AD47" s="3" t="n">
-        <v>9454545</v>
+        <v>13350812.98562836</v>
       </c>
       <c r="AE47" s="3" t="n">
         <v>107878595.7267165</v>
       </c>
       <c r="AF47" s="3" t="n">
-        <v>1881818</v>
+        <v>1771337.294256593</v>
       </c>
       <c r="AG47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH47" s="3" t="n">
-        <v>3727273</v>
+        <v>4428343.235641482</v>
       </c>
     </row>
     <row r="48">
@@ -5639,7 +5639,7 @@
         <v>18875894.36058085</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>31480000</v>
+        <v>43407741.54082263</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -5651,61 +5651,61 @@
         <v>15828647.41457528</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2740000</v>
+        <v>3782762.172032943</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>17836364</v>
+        <v>1080789.192009412</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>3240000</v>
+        <v>5403945.96004706</v>
       </c>
       <c r="U48" s="3" t="n">
         <v>18207978.09859106</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>2780000</v>
+        <v>4009486.270942149</v>
       </c>
       <c r="W48" s="3" t="n">
         <v>7811716.281532689</v>
       </c>
       <c r="X48" s="3" t="n">
-        <v>30410000</v>
+        <v>6966237.009565582</v>
       </c>
       <c r="Y48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>15496364</v>
+        <v>4063638.255579924</v>
       </c>
       <c r="AA48" s="3" t="n">
         <v>18875894.36058085</v>
       </c>
       <c r="AB48" s="3" t="n">
-        <v>30220000</v>
+        <v>44026255.1882177</v>
       </c>
       <c r="AC48" s="3" t="n">
         <v>421077.643428342</v>
       </c>
       <c r="AD48" s="3" t="n">
-        <v>2370000</v>
+        <v>5015289.507115584</v>
       </c>
       <c r="AE48" s="3" t="n">
         <v>1258392.957372057</v>
       </c>
       <c r="AF48" s="3" t="n">
-        <v>3300000</v>
+        <v>3921063.906727252</v>
       </c>
       <c r="AG48" s="3" t="n">
         <v>2516785.914744113</v>
       </c>
       <c r="AH48" s="3" t="n">
-        <v>15120000</v>
+        <v>16414325.26283048</v>
       </c>
     </row>
     <row r="49">
@@ -5753,25 +5753,25 @@
         <v>0</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>1240909</v>
+        <v>1217860.170484297</v>
       </c>
       <c r="O49" s="3" t="n">
         <v>15681512.23802101</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>2272728</v>
+        <v>2368057.182669309</v>
       </c>
       <c r="Q49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>14454547</v>
+        <v>16576400.27868517</v>
       </c>
       <c r="S49" s="3" t="n">
         <v>3519980.652339447</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>1240909</v>
+        <v>1178829.506780333</v>
       </c>
       <c r="U49" s="3" t="n">
         <v>0</v>
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="AH49" s="3" t="n">
-        <v>8363636</v>
+        <v>9430636.054242661</v>
       </c>
     </row>
     <row r="50">
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>7545455</v>
+        <v>4050874.734960276</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>0</v>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="3" t="n">
-        <v>33090911</v>
+        <v>44559622.08456304</v>
       </c>
       <c r="Y50" s="3" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
         <v>237599.1102705832</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>640909</v>
+        <v>2566992.594085851</v>
       </c>
       <c r="M51" s="3" t="n">
         <v>0</v>
@@ -5975,13 +5975,13 @@
         <v>0</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>618182</v>
+        <v>513398.5188171702</v>
       </c>
       <c r="Q51" s="3" t="n">
         <v>756795.5885743896</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>3009091</v>
+        <v>1514094.374173379</v>
       </c>
       <c r="S51" s="3" t="n">
         <v>439997.0975451395</v>
@@ -5999,37 +5999,37 @@
         <v>3431981.232830419</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>5909091</v>
+        <v>2206446.014573005</v>
       </c>
       <c r="Y51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>590909</v>
+        <v>551611.5036432513</v>
       </c>
       <c r="AA51" s="3" t="n">
         <v>1487192.028892279</v>
       </c>
       <c r="AB51" s="3" t="n">
-        <v>3836364</v>
+        <v>2866289.991372559</v>
       </c>
       <c r="AC51" s="3" t="n">
         <v>2719153.894186609</v>
       </c>
       <c r="AD51" s="3" t="n">
-        <v>2481818</v>
+        <v>674329.1137044274</v>
       </c>
       <c r="AE51" s="3" t="n">
         <v>3054021.940089139</v>
       </c>
       <c r="AF51" s="3" t="n">
-        <v>627273</v>
+        <v>347911.7721364921</v>
       </c>
       <c r="AG51" s="3" t="n">
         <v>26888249.78323152</v>
       </c>
       <c r="AH51" s="3" t="n">
-        <v>409091</v>
+        <v>452994.3093319844</v>
       </c>
     </row>
     <row r="52">
@@ -6071,73 +6071,73 @@
         <v>5851968.657309726</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>5460000</v>
+        <v>5629649.61461867</v>
       </c>
       <c r="M52" s="3" t="n">
         <v>3079982.586799724</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>2327274</v>
+        <v>527504.9765193271</v>
       </c>
       <c r="O52" s="3" t="n">
         <v>8007955.887272784</v>
       </c>
       <c r="P52" s="3" t="n">
-        <v>3136367</v>
+        <v>4389940.262008117</v>
       </c>
       <c r="Q52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R52" s="3" t="n">
-        <v>4100000</v>
+        <v>2605683.767212234</v>
       </c>
       <c r="S52" s="3" t="n">
         <v>5367970.398018198</v>
       </c>
       <c r="T52" s="3" t="n">
-        <v>5927274</v>
+        <v>4779576.721544819</v>
       </c>
       <c r="U52" s="3" t="n">
         <v>7567958.770367753</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>5981820</v>
+        <v>3792088.806920809</v>
       </c>
       <c r="W52" s="3" t="n">
         <v>5614367.611049977</v>
       </c>
       <c r="X52" s="3" t="n">
-        <v>10636370</v>
+        <v>3913808.049274529</v>
       </c>
       <c r="Y52" s="3" t="n">
         <v>5738095.710602545</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>1745455</v>
+        <v>1964619.49462701</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>6398091.840917546</v>
       </c>
       <c r="AB52" s="3" t="n">
-        <v>7609092</v>
+        <v>6048702.22686644</v>
       </c>
       <c r="AC52" s="3" t="n">
         <v>15523111.54051451</v>
       </c>
       <c r="AD52" s="3" t="n">
-        <v>3863638</v>
+        <v>6470995.138044011</v>
       </c>
       <c r="AE52" s="3" t="n">
         <v>18603096.0633034</v>
       </c>
       <c r="AF52" s="3" t="n">
-        <v>8436365</v>
+        <v>6091997.158825203</v>
       </c>
       <c r="AG52" s="3" t="n">
         <v>160317501.9870543</v>
       </c>
       <c r="AH52" s="3" t="n">
-        <v>43277273</v>
+        <v>24772631.27677104</v>
       </c>
     </row>
     <row r="53">
